--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2019_aysen.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2019_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 13:39</t>
+    <t xml:space="preserve">2026-09-09 19:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2019_aysen.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2019_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:57</t>
+    <t xml:space="preserve">2026-09-18 17:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2019_aysen.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2019_aysen.xlsx
@@ -30,36 +30,36 @@
     <t xml:space="preserve">Cobertura</t>
   </si>
   <si>
+    <t xml:space="preserve">Aysén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chile Chico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coyhaique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guaitecas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cochrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O'Higgins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Río Ibáñez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tortel</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lago Verde</t>
   </si>
   <si>
-    <t xml:space="preserve">Tortel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Río Ibáñez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O'Higgins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisnes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cochrane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guaitecas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coyhaique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chile Chico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 17:03</t>
+    <t xml:space="preserve">2026-09-27 21:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -489,13 +489,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>751</v>
+        <v>26512</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>919</v>
+        <v>24880</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>81.72</v>
+        <v>106.56</v>
       </c>
     </row>
     <row r="3">
@@ -503,13 +503,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>492</v>
+        <v>5365</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>567</v>
+        <v>5096</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>86.77</v>
+        <v>105.28</v>
       </c>
     </row>
     <row r="4">
@@ -517,13 +517,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2424</v>
+        <v>61803</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2689</v>
+        <v>60822</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>90.15</v>
+        <v>101.61</v>
       </c>
     </row>
     <row r="5">
@@ -531,13 +531,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>618</v>
+        <v>1598</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>655</v>
+        <v>1591</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>94.35</v>
+        <v>100.44</v>
       </c>
     </row>
     <row r="6">
@@ -545,13 +545,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>5512</v>
+        <v>3655</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>5801</v>
+        <v>3660</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>95.02</v>
+        <v>99.86</v>
       </c>
     </row>
     <row r="7">
@@ -559,13 +559,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>3655</v>
+        <v>5512</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>3660</v>
+        <v>5801</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>99.86</v>
+        <v>95.02</v>
       </c>
     </row>
     <row r="8">
@@ -573,13 +573,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1598</v>
+        <v>618</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1591</v>
+        <v>655</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>100.44</v>
+        <v>94.35</v>
       </c>
     </row>
     <row r="9">
@@ -587,13 +587,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>61803</v>
+        <v>2424</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>60822</v>
+        <v>2689</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>101.61</v>
+        <v>90.15</v>
       </c>
     </row>
     <row r="10">
@@ -601,13 +601,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>5365</v>
+        <v>492</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>5096</v>
+        <v>567</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>105.28</v>
+        <v>86.77</v>
       </c>
     </row>
     <row r="11">
@@ -615,13 +615,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>26512</v>
+        <v>751</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>24880</v>
+        <v>919</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>106.56</v>
+        <v>81.72</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2019_aysen.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2019_aysen.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 21:45</t>
+    <t xml:space="preserve">2026-10-05 05:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
